--- a/ExcelRAddIn/Tests/R Types Tests.xlsx
+++ b/ExcelRAddIn/Tests/R Types Tests.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D96B91-A8A0-49D2-B6D6-5626EB00057E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4803220B-26C8-4002-B38D-0CF91BCA584E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="852" firstSheet="10" activeTab="19" xr2:uid="{5877FA5A-76F9-4C4A-95F7-F8E57366BB43}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="852" firstSheet="11" activeTab="20" xr2:uid="{5877FA5A-76F9-4C4A-95F7-F8E57366BB43}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary Types" sheetId="18" r:id="rId1"/>
@@ -931,8 +931,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000E+00"/>
+    <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -969,7 +970,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -986,6 +987,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1392,43 +1394,43 @@
       </c>
       <c r="F2" cm="1">
         <f t="array" ref="F2">_xll.RScript.Evaluate($E$2&amp;"["&amp;F1&amp;"]")</f>
-        <v>-1.1880159611636512</v>
+        <v>1.3240337372279194</v>
       </c>
       <c r="G2" cm="1">
         <f t="array" ref="G2">_xll.RScript.Evaluate($E$2&amp;"["&amp;G1&amp;"]")</f>
-        <v>-0.14831709096571422</v>
+        <v>1.0979278137623114</v>
       </c>
       <c r="H2" cm="1">
         <f t="array" ref="H2">_xll.RScript.Evaluate($E$2&amp;"["&amp;H1&amp;"]")</f>
-        <v>0.39898072850752042</v>
+        <v>2.7368080366415684</v>
       </c>
       <c r="I2" cm="1">
         <f t="array" ref="I2">_xll.RScript.Evaluate($E$2&amp;"["&amp;I1&amp;"]")</f>
-        <v>0.12325104199573529</v>
+        <v>-0.41720002480180213</v>
       </c>
       <c r="J2" cm="1">
         <f t="array" ref="J2">_xll.RScript.Evaluate($E$2&amp;"["&amp;J1&amp;"]")</f>
-        <v>0.66194300195975542</v>
+        <v>0.33620532746774823</v>
       </c>
       <c r="K2" cm="1">
         <f t="array" ref="K2">_xll.RScript.Evaluate($E$2&amp;"["&amp;K1&amp;"]")</f>
-        <v>0.66681371838657433</v>
+        <v>0.66450062094704399</v>
       </c>
       <c r="L2" cm="1">
         <f t="array" ref="L2">_xll.RScript.Evaluate($E$2&amp;"["&amp;L1&amp;"]")</f>
-        <v>-1.5209845574473024</v>
+        <v>-0.56786204234787019</v>
       </c>
       <c r="M2" cm="1">
         <f t="array" ref="M2">_xll.RScript.Evaluate($E$2&amp;"["&amp;M1&amp;"]")</f>
-        <v>-0.19923384758078849</v>
+        <v>-0.1504497188607187</v>
       </c>
       <c r="N2" cm="1">
         <f t="array" ref="N2">_xll.RScript.Evaluate($E$2&amp;"["&amp;N1&amp;"]")</f>
-        <v>0.20190649829949189</v>
+        <v>-0.86852408731795083</v>
       </c>
       <c r="O2" cm="1">
         <f t="array" ref="O2">_xll.RScript.Evaluate($E$2&amp;"["&amp;O1&amp;"]")</f>
-        <v>-0.44047867839884547</v>
+        <v>1.2657178018493058</v>
       </c>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.3">
@@ -1548,43 +1550,43 @@
       </c>
       <c r="F5" t="str" cm="1">
         <f t="array" ref="F5">_xll.RScript.Evaluate($E$5&amp;"["&amp;F1&amp;"]")</f>
-        <v>-0.333705621073604+0.639802141545883i</v>
+        <v>3.25462705829063-0.181058194366586i</v>
       </c>
       <c r="G5" t="str" cm="1">
         <f t="array" ref="G5">_xll.RScript.Evaluate($E$5&amp;"["&amp;G1&amp;"]")</f>
-        <v>0.462919588283699-0.700618026485648i</v>
+        <v>-1.50736642863886+1.35589028687698i</v>
       </c>
       <c r="H5" t="str" cm="1">
         <f t="array" ref="H5">_xll.RScript.Evaluate($E$5&amp;"["&amp;H1&amp;"]")</f>
-        <v>0.376810911043259+2.25697250809625i</v>
+        <v>-0.267373674323065+0.819701467499229i</v>
       </c>
       <c r="I5" t="str" cm="1">
         <f t="array" ref="I5">_xll.RScript.Evaluate($E$5&amp;"["&amp;I1&amp;"]")</f>
-        <v>0.534028526624503+1.22188980902137i</v>
+        <v>0.242643350255135-0.131267194697746i</v>
       </c>
       <c r="J5" t="str" cm="1">
         <f t="array" ref="J5">_xll.RScript.Evaluate($E$5&amp;"["&amp;J1&amp;"]")</f>
-        <v>2.36514333388565-0.401828513903769i</v>
+        <v>-0.380844163320368-0.526129040089019i</v>
       </c>
       <c r="K5" t="str" cm="1">
         <f t="array" ref="K5">_xll.RScript.Evaluate($E$5&amp;"["&amp;K1&amp;"]")</f>
-        <v>-0.17272202036455+0.368944610077771i</v>
+        <v>0.55432038906876+1.25181114949516i</v>
       </c>
       <c r="L5" t="str" cm="1">
         <f t="array" ref="L5">_xll.RScript.Evaluate($E$5&amp;"["&amp;L1&amp;"]")</f>
-        <v>0.0241603518073429-0.866381113796704i</v>
+        <v>0.292836431334466-1.73165165437344i</v>
       </c>
       <c r="M5" t="str" cm="1">
         <f t="array" ref="M5">_xll.RScript.Evaluate($E$5&amp;"["&amp;M1&amp;"]")</f>
-        <v>-0.0831477635497377-0.88714291903732i</v>
+        <v>0.935473000766626+0.56071701468096i</v>
       </c>
       <c r="N5" t="str" cm="1">
         <f t="array" ref="N5">_xll.RScript.Evaluate($E$5&amp;"["&amp;N1&amp;"]")</f>
-        <v>-0.193696321186678+0.314861612732435i</v>
+        <v>1.09434151478318-0.25606965869265i</v>
       </c>
       <c r="O5" t="str" cm="1">
         <f t="array" ref="O5">_xll.RScript.Evaluate($E$5&amp;"["&amp;O1&amp;"]")</f>
-        <v>-2.19699868926359-1.79484425996288i</v>
+        <v>0.575182889798066+2.04143436276556i</v>
       </c>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.3">
@@ -1721,34 +1723,34 @@
       </c>
       <c r="H15" cm="1">
         <f t="array" ref="H15:Q15">TRANSPOSE(_xll.RScript.Evaluate(G15))</f>
-        <v>-1.0579444978294112</v>
+        <v>1.3240337372279194</v>
       </c>
       <c r="I15">
-        <v>-0.34675700843334811</v>
+        <v>1.0979278137623114</v>
       </c>
       <c r="J15">
-        <v>-1.3914632267915907</v>
+        <v>2.7368080366415684</v>
       </c>
       <c r="K15">
-        <v>-0.51979432070762666</v>
+        <v>-0.41720002480180213</v>
       </c>
       <c r="L15">
-        <v>-0.26026432623747425</v>
+        <v>0.33620532746774823</v>
       </c>
       <c r="M15">
-        <v>-1.8307278764434405</v>
+        <v>0.66450062094704399</v>
       </c>
       <c r="N15">
-        <v>1.038726491394004</v>
+        <v>-0.56786204234787019</v>
       </c>
       <c r="O15">
-        <v>0.24997500890044486</v>
+        <v>-0.1504497188607187</v>
       </c>
       <c r="P15">
-        <v>0.2799300143278371</v>
+        <v>-0.86852408731795083</v>
       </c>
       <c r="Q15">
-        <v>-0.49092292086657291</v>
+        <v>1.2657178018493058</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.3">
@@ -1760,34 +1762,34 @@
       </c>
       <c r="H16" cm="1">
         <f t="array" ref="H16:Q16">TRANSPOSE(_xll.RScript.Evaluate(G16))</f>
-        <v>-1.0579444978294112</v>
+        <v>1.3240337372279194</v>
       </c>
       <c r="I16">
-        <v>-0.34675700843334811</v>
+        <v>1.0979278137623114</v>
       </c>
       <c r="J16">
-        <v>-1.3914632267915907</v>
+        <v>2.7368080366415684</v>
       </c>
       <c r="K16">
-        <v>-0.51979432070762666</v>
+        <v>-0.41720002480180213</v>
       </c>
       <c r="L16">
-        <v>-0.26026432623747425</v>
+        <v>0.33620532746774823</v>
       </c>
       <c r="M16">
-        <v>-1.8307278764434405</v>
+        <v>0.66450062094704399</v>
       </c>
       <c r="N16">
-        <v>1.038726491394004</v>
+        <v>-0.56786204234787019</v>
       </c>
       <c r="O16">
-        <v>0.24997500890044486</v>
+        <v>-0.1504497188607187</v>
       </c>
       <c r="P16">
-        <v>0.2799300143278371</v>
+        <v>-0.86852408731795083</v>
       </c>
       <c r="Q16">
-        <v>-0.49092292086657291</v>
+        <v>1.2657178018493058</v>
       </c>
     </row>
     <row r="17" spans="4:4" x14ac:dyDescent="0.3">
@@ -5167,19 +5169,19 @@
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D3" s="5" t="str" cm="1">
         <f t="array" ref="D3:D102">_xll.RScript.Evaluate(D2)</f>
-        <v>0.0479905174497235+0.518181973481806i</v>
+        <v>-0.380423381850074+0.370005314274227i</v>
       </c>
       <c r="E3">
         <f>IMREAL(D3)</f>
-        <v>4.7990517449723498E-2</v>
+        <v>-0.38042338185007402</v>
       </c>
       <c r="F3">
         <f>IMAGINARY(D3)</f>
-        <v>0.51818197348180595</v>
+        <v>0.370005314274227</v>
       </c>
       <c r="G3" t="str">
         <f>COMPLEX(ROUND(E3, $G$2), ROUND(F3, $G$2))</f>
-        <v>0.0479905174497235+0.518181973481806i</v>
+        <v>-0.380423381850074+0.370005314274227i</v>
       </c>
       <c r="H3" t="str">
         <f>IF(G3=D3, "OK", "FAIL")</f>
@@ -5189,19 +5191,19 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D4" s="3" t="str">
-        <v>0.41630360813961+0.224102007091764i</v>
+        <v>3.59511899426475+0.195521244055853i</v>
       </c>
       <c r="E4">
         <f t="shared" ref="E4:E67" si="0">IMREAL(D4)</f>
-        <v>0.41630360813960998</v>
+        <v>3.5951189942647499</v>
       </c>
       <c r="F4">
         <f t="shared" ref="F4:F67" si="1">IMAGINARY(D4)</f>
-        <v>0.22410200709176401</v>
+        <v>0.195521244055853</v>
       </c>
       <c r="G4" t="str">
         <f t="shared" ref="G4:G67" si="2">COMPLEX(ROUND(E4, $G$2), ROUND(F4, $G$2))</f>
-        <v>0.41630360813961+0.224102007091764i</v>
+        <v>3.59511899426475+0.195521244055853i</v>
       </c>
       <c r="H4" t="str">
         <f t="shared" ref="H4:H67" si="3">IF(G4=D4, "OK", "FAIL")</f>
@@ -5210,19 +5212,19 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D5" s="3" t="str">
-        <v>-2.16135319790637+1.38872398833955i</v>
+        <v>1.42906660817829-1.69858996526513i</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>-2.16135319790637</v>
+        <v>1.4290666081782899</v>
       </c>
       <c r="F5">
         <f t="shared" si="1"/>
-        <v>1.3887239883395499</v>
+        <v>-1.69858996526513</v>
       </c>
       <c r="G5" t="str">
         <f t="shared" si="2"/>
-        <v>-2.16135319790637+1.38872398833955i</v>
+        <v>1.42906660817829-1.69858996526513i</v>
       </c>
       <c r="H5" t="str">
         <f t="shared" si="3"/>
@@ -5231,19 +5233,19 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D6" s="3" t="str">
-        <v>1.12169004191356-1.4054260558242i</v>
+        <v>-0.179316728266741-0.3616683722835i</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>1.12169004191356</v>
+        <v>-0.179316728266741</v>
       </c>
       <c r="F6">
         <f t="shared" si="1"/>
-        <v>-1.4054260558242</v>
+        <v>-0.36166837228350002</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="2"/>
-        <v>1.12169004191356-1.4054260558242i</v>
+        <v>-0.179316728266741-0.3616683722835i</v>
       </c>
       <c r="H6" t="str">
         <f t="shared" si="3"/>
@@ -5252,19 +5254,19 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D7" s="3" t="str">
-        <v>0.730916634347569-1.58472749187273i</v>
+        <v>-0.23722173498805-0.478406593669504i</v>
       </c>
       <c r="E7">
         <f t="shared" si="0"/>
-        <v>0.73091663434756904</v>
+        <v>-0.23722173498804999</v>
       </c>
       <c r="F7">
         <f t="shared" si="1"/>
-        <v>-1.5847274918727301</v>
+        <v>-0.478406593669504</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="2"/>
-        <v>0.730916634347569-1.58472749187273i</v>
+        <v>-0.23722173498805-0.478406593669504i</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="3"/>
@@ -5273,19 +5275,19 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D8" s="3" t="str">
-        <v>-0.100120789511854+0.91555077592385i</v>
+        <v>-0.150060373453254-1.17796267178894i</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>-0.10012078951185401</v>
+        <v>-0.15006037345325399</v>
       </c>
       <c r="F8">
         <f t="shared" si="1"/>
-        <v>0.91555077592385004</v>
+        <v>-1.17796267178894</v>
       </c>
       <c r="G8" t="str">
         <f t="shared" si="2"/>
-        <v>-0.100120789511854+0.91555077592385i</v>
+        <v>-0.150060373453254-1.17796267178894i</v>
       </c>
       <c r="H8" t="str">
         <f t="shared" si="3"/>
@@ -5294,19 +5296,19 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D9" s="3" t="str">
-        <v>-0.561130847223455+0.129744210006769i</v>
+        <v>1.6723111706226-0.113664607078772i</v>
       </c>
       <c r="E9">
         <f t="shared" si="0"/>
-        <v>-0.56113084722345496</v>
+        <v>1.6723111706225999</v>
       </c>
       <c r="F9">
         <f t="shared" si="1"/>
-        <v>0.129744210006769</v>
+        <v>-0.113664607078772</v>
       </c>
       <c r="G9" t="str">
         <f t="shared" si="2"/>
-        <v>-0.561130847223455+0.129744210006769i</v>
+        <v>1.6723111706226-0.113664607078772i</v>
       </c>
       <c r="H9" t="str">
         <f t="shared" si="3"/>
@@ -5315,19 +5317,19 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D10" s="3" t="str">
-        <v>1.40193347847784-0.426176728505478i</v>
+        <v>-0.632236699831206+1.68151658713129i</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>1.4019334784778399</v>
+        <v>-0.63223669983120601</v>
       </c>
       <c r="F10">
         <f t="shared" si="1"/>
-        <v>-0.426176728505478</v>
+        <v>1.68151658713129</v>
       </c>
       <c r="G10" t="str">
         <f t="shared" si="2"/>
-        <v>1.40193347847784-0.426176728505478i</v>
+        <v>-0.632236699831206+1.68151658713129i</v>
       </c>
       <c r="H10" t="str">
         <f t="shared" si="3"/>
@@ -5336,19 +5338,19 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D11" s="3" t="str">
-        <v>-0.938851095263297-0.118537251853665i</v>
+        <v>-0.363043758755356-0.271958718499594i</v>
       </c>
       <c r="E11">
         <f t="shared" si="0"/>
-        <v>-0.93885109526329702</v>
+        <v>-0.36304375875535599</v>
       </c>
       <c r="F11">
         <f t="shared" si="1"/>
-        <v>-0.118537251853665</v>
+        <v>-0.27195871849959402</v>
       </c>
       <c r="G11" t="str">
         <f t="shared" si="2"/>
-        <v>-0.938851095263297-0.118537251853665i</v>
+        <v>-0.363043758755356-0.271958718499594i</v>
       </c>
       <c r="H11" t="str">
         <f t="shared" si="3"/>
@@ -5357,19 +5359,19 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D12" s="3" t="str">
-        <v>-0.548629066875611+0.251682817228076i</v>
+        <v>-0.462046057512136+1.79945511384139i</v>
       </c>
       <c r="E12">
         <f t="shared" si="0"/>
-        <v>-0.54862906687561097</v>
+        <v>-0.46204605751213601</v>
       </c>
       <c r="F12">
         <f t="shared" si="1"/>
-        <v>0.25168281722807601</v>
+        <v>1.7994551138413899</v>
       </c>
       <c r="G12" t="str">
         <f t="shared" si="2"/>
-        <v>-0.548629066875611+0.251682817228076i</v>
+        <v>-0.462046057512136+1.79945511384139i</v>
       </c>
       <c r="H12" t="str">
         <f t="shared" si="3"/>
@@ -5378,19 +5380,19 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D13" s="3" t="str">
-        <v>-0.385891288809405-0.590130218385907i</v>
+        <v>1.50374458370141-0.0126746610743221i</v>
       </c>
       <c r="E13">
         <f t="shared" si="0"/>
-        <v>-0.38589128880940499</v>
+        <v>1.5037445837014101</v>
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
-        <v>-0.59013021838590696</v>
+        <v>-1.2674661074322101E-2</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="2"/>
-        <v>-0.385891288809405-0.590130218385907i</v>
+        <v>1.50374458370141-0.0126746610743221i</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="3"/>
@@ -5399,19 +5401,19 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D14" s="3" t="str">
-        <v>-0.243894908875301-0.223774844603452i</v>
+        <v>0.265575610725953-0.0629762082573113i</v>
       </c>
       <c r="E14">
         <f t="shared" si="0"/>
-        <v>-0.24389490887530099</v>
+        <v>0.26557561072595298</v>
       </c>
       <c r="F14">
         <f t="shared" si="1"/>
-        <v>-0.22377484460345201</v>
+        <v>-6.2976208257311303E-2</v>
       </c>
       <c r="G14" t="str">
         <f t="shared" si="2"/>
-        <v>-0.243894908875301-0.223774844603452i</v>
+        <v>0.265575610725953-0.0629762082573113i</v>
       </c>
       <c r="H14" t="str">
         <f t="shared" si="3"/>
@@ -5420,19 +5422,19 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D15" s="3" t="str">
-        <v>-0.494987789009149+1.6223238799813i</v>
+        <v>0.228273769787887-0.203001376885616i</v>
       </c>
       <c r="E15">
         <f t="shared" si="0"/>
-        <v>-0.49498778900914903</v>
+        <v>0.22827376978788699</v>
       </c>
       <c r="F15">
         <f t="shared" si="1"/>
-        <v>1.6223238799813</v>
+        <v>-0.20300137688561601</v>
       </c>
       <c r="G15" t="str">
         <f t="shared" si="2"/>
-        <v>-0.494987789009149+1.6223238799813i</v>
+        <v>0.228273769787887-0.203001376885616i</v>
       </c>
       <c r="H15" t="str">
         <f t="shared" si="3"/>
@@ -5441,19 +5443,19 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D16" s="3" t="str">
-        <v>-1.42915086556801-0.994217896085889i</v>
+        <v>0.998186302266315+0.650621605716463i</v>
       </c>
       <c r="E16">
         <f t="shared" si="0"/>
-        <v>-1.4291508655680101</v>
+        <v>0.998186302266315</v>
       </c>
       <c r="F16">
         <f t="shared" si="1"/>
-        <v>-0.99421789608588895</v>
+        <v>0.65062160571646299</v>
       </c>
       <c r="G16" t="str">
         <f t="shared" si="2"/>
-        <v>-1.42915086556801-0.994217896085889i</v>
+        <v>0.998186302266315+0.650621605716463i</v>
       </c>
       <c r="H16" t="str">
         <f t="shared" si="3"/>
@@ -5462,19 +5464,19 @@
     </row>
     <row r="17" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D17" s="3" t="str">
-        <v>-0.98955428966825+0.883978407533478i</v>
+        <v>0.503883834371391+0.283933017648257i</v>
       </c>
       <c r="E17">
         <f t="shared" si="0"/>
-        <v>-0.98955428966824999</v>
+        <v>0.50388383437139095</v>
       </c>
       <c r="F17">
         <f t="shared" si="1"/>
-        <v>0.88397840753347801</v>
+        <v>0.28393301764825701</v>
       </c>
       <c r="G17" t="str">
         <f t="shared" si="2"/>
-        <v>-0.98955428966825+0.883978407533478i</v>
+        <v>0.503883834371391+0.283933017648257i</v>
       </c>
       <c r="H17" t="str">
         <f t="shared" si="3"/>
@@ -5483,19 +5485,19 @@
     </row>
     <row r="18" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D18" s="3" t="str">
-        <v>-1.60186582824293+0.165405463985982i</v>
+        <v>0.500682313768012-1.07527042770102i</v>
       </c>
       <c r="E18">
         <f t="shared" si="0"/>
-        <v>-1.6018658282429299</v>
+        <v>0.50068231376801198</v>
       </c>
       <c r="F18">
         <f t="shared" si="1"/>
-        <v>0.16540546398598199</v>
+        <v>-1.0752704277010201</v>
       </c>
       <c r="G18" t="str">
         <f t="shared" si="2"/>
-        <v>-1.60186582824293+0.165405463985982i</v>
+        <v>0.500682313768012-1.07527042770102i</v>
       </c>
       <c r="H18" t="str">
         <f t="shared" si="3"/>
@@ -5504,19 +5506,19 @@
     </row>
     <row r="19" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D19" s="3" t="str">
-        <v>1.83082012911555-0.0276470223530829i</v>
+        <v>0.255921539368493+0.205800511039202i</v>
       </c>
       <c r="E19">
         <f t="shared" si="0"/>
-        <v>1.8308201291155499</v>
+        <v>0.25592153936849299</v>
       </c>
       <c r="F19">
         <f t="shared" si="1"/>
-        <v>-2.76470223530829E-2</v>
+        <v>0.20580051103920199</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>1.83082012911555-0.0276470223530829i</v>
+        <v>0.255921539368493+0.205800511039202i</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="3"/>
@@ -5525,19 +5527,19 @@
     </row>
     <row r="20" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D20" s="3" t="str">
-        <v>-2.19599607952415+0.00048952366238532i</v>
+        <v>1.50963376364605-0.228475918514487i</v>
       </c>
       <c r="E20">
         <f t="shared" si="0"/>
-        <v>-2.19599607952415</v>
+        <v>1.50963376364605</v>
       </c>
       <c r="F20">
         <f t="shared" si="1"/>
-        <v>4.8952366238532005E-4</v>
+        <v>-0.22847591851448701</v>
       </c>
       <c r="G20" t="str">
         <f t="shared" si="2"/>
-        <v>-2.19599607952415+0.00048952366238532i</v>
+        <v>1.50963376364605-0.228475918514487i</v>
       </c>
       <c r="H20" t="str">
         <f t="shared" si="3"/>
@@ -5546,19 +5548,19 @@
     </row>
     <row r="21" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D21" s="3" t="str">
-        <v>-1.07340346185614+1.49725358445492i</v>
+        <v>1.00725817912583+0.235887153632737i</v>
       </c>
       <c r="E21">
         <f t="shared" si="0"/>
-        <v>-1.0734034618561401</v>
+        <v>1.0072581791258299</v>
       </c>
       <c r="F21">
         <f t="shared" si="1"/>
-        <v>1.49725358445492</v>
+        <v>0.23588715363273699</v>
       </c>
       <c r="G21" t="str">
         <f t="shared" si="2"/>
-        <v>-1.07340346185614+1.49725358445492i</v>
+        <v>1.00725817912583+0.235887153632737i</v>
       </c>
       <c r="H21" t="str">
         <f t="shared" si="3"/>
@@ -5567,19 +5569,19 @@
     </row>
     <row r="22" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D22" s="3" t="str">
-        <v>-1.37520256550754+1.90186243191226i</v>
+        <v>-0.436480929090423-0.53831112157763i</v>
       </c>
       <c r="E22">
         <f t="shared" si="0"/>
-        <v>-1.3752025655075399</v>
+        <v>-0.43648092909042302</v>
       </c>
       <c r="F22">
         <f t="shared" si="1"/>
-        <v>1.9018624319122599</v>
+        <v>-0.53831112157762995</v>
       </c>
       <c r="G22" t="str">
         <f t="shared" si="2"/>
-        <v>-1.37520256550754+1.90186243191226i</v>
+        <v>-0.436480929090423-0.53831112157763i</v>
       </c>
       <c r="H22" t="str">
         <f t="shared" si="3"/>
@@ -5588,19 +5590,19 @@
     </row>
     <row r="23" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D23" s="3" t="str">
-        <v>-0.624801376864602+0.135946357594546i</v>
+        <v>0.586377957100549-1.0373561335326i</v>
       </c>
       <c r="E23">
         <f t="shared" si="0"/>
-        <v>-0.62480137686460202</v>
+        <v>0.58637795710054896</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
-        <v>0.13594635759454601</v>
+        <v>-1.0373561335326</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" si="2"/>
-        <v>-0.624801376864602+0.135946357594546i</v>
+        <v>0.586377957100549-1.0373561335326i</v>
       </c>
       <c r="H23" t="str">
         <f t="shared" si="3"/>
@@ -5609,19 +5611,19 @@
     </row>
     <row r="24" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D24" s="3" t="str">
-        <v>0.473055122464588-0.88190583121716i</v>
+        <v>0.826315947781413+0.863647273356401i</v>
       </c>
       <c r="E24">
         <f t="shared" si="0"/>
-        <v>0.47305512246458797</v>
+        <v>0.82631594778141304</v>
       </c>
       <c r="F24">
         <f t="shared" si="1"/>
-        <v>-0.88190583121716004</v>
+        <v>0.86364727335640101</v>
       </c>
       <c r="G24" t="str">
         <f t="shared" si="2"/>
-        <v>0.473055122464588-0.88190583121716i</v>
+        <v>0.826315947781413+0.863647273356401i</v>
       </c>
       <c r="H24" t="str">
         <f t="shared" si="3"/>
@@ -5630,19 +5632,19 @@
     </row>
     <row r="25" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D25" s="3" t="str">
-        <v>1.10864864566934+0.60791217721878i</v>
+        <v>-1.86784163385986-0.204628899911475i</v>
       </c>
       <c r="E25">
         <f t="shared" si="0"/>
-        <v>1.1086486456693401</v>
+        <v>-1.86784163385986</v>
       </c>
       <c r="F25">
         <f t="shared" si="1"/>
-        <v>0.60791217721877999</v>
+        <v>-0.20462889991147501</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="2"/>
-        <v>1.10864864566934+0.60791217721878i</v>
+        <v>-1.86784163385986-0.204628899911475i</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
@@ -5651,19 +5653,19 @@
     </row>
     <row r="26" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D26" s="3" t="str">
-        <v>-2.49960541482281+1.48499832143048i</v>
+        <v>-1.02033505933274+0.439201895012886i</v>
       </c>
       <c r="E26">
         <f t="shared" si="0"/>
-        <v>-2.4996054148228102</v>
+        <v>-1.02033505933274</v>
       </c>
       <c r="F26">
         <f t="shared" si="1"/>
-        <v>1.4849983214304801</v>
+        <v>0.43920189501288598</v>
       </c>
       <c r="G26" t="str">
         <f t="shared" si="2"/>
-        <v>-2.49960541482281+1.48499832143048i</v>
+        <v>-1.02033505933274+0.439201895012886i</v>
       </c>
       <c r="H26" t="str">
         <f t="shared" si="3"/>
@@ -5672,19 +5674,19 @@
     </row>
     <row r="27" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D27" s="3" t="str">
-        <v>-0.224396709833206+2.23368064654137i</v>
+        <v>0.220789635032726+0.0877017609173915i</v>
       </c>
       <c r="E27">
         <f t="shared" si="0"/>
-        <v>-0.224396709833206</v>
+        <v>0.220789635032726</v>
       </c>
       <c r="F27">
         <f t="shared" si="1"/>
-        <v>2.2336806465413699</v>
+        <v>8.77017609173915E-2</v>
       </c>
       <c r="G27" t="str">
         <f t="shared" si="2"/>
-        <v>-0.224396709833206+2.23368064654137i</v>
+        <v>0.220789635032726+0.0877017609173915i</v>
       </c>
       <c r="H27" t="str">
         <f t="shared" si="3"/>
@@ -5693,19 +5695,19 @@
     </row>
     <row r="28" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D28" s="3" t="str">
-        <v>-0.507765544129998+0.249318792201103i</v>
+        <v>-1.04670402167935+0.70120741280245i</v>
       </c>
       <c r="E28">
         <f t="shared" si="0"/>
-        <v>-0.50776554412999797</v>
+        <v>-1.0467040216793499</v>
       </c>
       <c r="F28">
         <f t="shared" si="1"/>
-        <v>0.24931879220110301</v>
+        <v>0.70120741280245003</v>
       </c>
       <c r="G28" t="str">
         <f t="shared" si="2"/>
-        <v>-0.507765544129998+0.249318792201103i</v>
+        <v>-1.04670402167935+0.70120741280245i</v>
       </c>
       <c r="H28" t="str">
         <f t="shared" si="3"/>
@@ -5714,19 +5716,19 @@
     </row>
     <row r="29" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D29" s="3" t="str">
-        <v>-1.45005885911665+2.03160552321533i</v>
+        <v>0.447021982118156+0.392113991219236i</v>
       </c>
       <c r="E29">
         <f t="shared" si="0"/>
-        <v>-1.4500588591166499</v>
+        <v>0.44702198211815602</v>
       </c>
       <c r="F29">
         <f t="shared" si="1"/>
-        <v>2.0316055232153301</v>
+        <v>0.39211399121923601</v>
       </c>
       <c r="G29" t="str">
         <f t="shared" si="2"/>
-        <v>-1.45005885911665+2.03160552321533i</v>
+        <v>0.447021982118156+0.392113991219236i</v>
       </c>
       <c r="H29" t="str">
         <f t="shared" si="3"/>
@@ -5735,19 +5737,19 @@
     </row>
     <row r="30" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D30" s="3" t="str">
-        <v>0.520790746606167+1.69105542480424i</v>
+        <v>-0.388824741301795+1.30274261574621i</v>
       </c>
       <c r="E30">
         <f t="shared" si="0"/>
-        <v>0.52079074660616698</v>
+        <v>-0.38882474130179501</v>
       </c>
       <c r="F30">
         <f t="shared" si="1"/>
-        <v>1.69105542480424</v>
+        <v>1.3027426157462101</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="2"/>
-        <v>0.520790746606167+1.69105542480424i</v>
+        <v>-0.388824741301795+1.30274261574621i</v>
       </c>
       <c r="H30" t="str">
         <f t="shared" si="3"/>
@@ -5756,19 +5758,19 @@
     </row>
     <row r="31" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D31" s="3" t="str">
-        <v>1.48671340719784+1.50758500416603i</v>
+        <v>-1.10414160256763+0.854070652296215i</v>
       </c>
       <c r="E31">
         <f t="shared" si="0"/>
-        <v>1.4867134071978401</v>
+        <v>-1.1041416025676301</v>
       </c>
       <c r="F31">
         <f t="shared" si="1"/>
-        <v>1.5075850041660299</v>
+        <v>0.85407065229621504</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="2"/>
-        <v>1.48671340719784+1.50758500416603i</v>
+        <v>-1.10414160256763+0.854070652296215i</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="3"/>
@@ -5777,19 +5779,19 @@
     </row>
     <row r="32" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D32" s="3" t="str">
-        <v>2.47116416528216-0.093501936598943i</v>
+        <v>-1.015973727277-1.60113818847017i</v>
       </c>
       <c r="E32">
         <f t="shared" si="0"/>
-        <v>2.4711641652821599</v>
+        <v>-1.015973727277</v>
       </c>
       <c r="F32">
         <f t="shared" si="1"/>
-        <v>-9.3501936598943E-2</v>
+        <v>-1.6011381884701701</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="2"/>
-        <v>2.47116416528216-0.093501936598943i</v>
+        <v>-1.015973727277-1.60113818847017i</v>
       </c>
       <c r="H32" t="str">
         <f t="shared" si="3"/>
@@ -5798,19 +5800,19 @@
     </row>
     <row r="33" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D33" s="3" t="str">
-        <v>-0.361018438089309-0.278669593943642i</v>
+        <v>0.218754879547233+2.33915110109041i</v>
       </c>
       <c r="E33">
         <f t="shared" si="0"/>
-        <v>-0.361018438089309</v>
+        <v>0.21875487954723299</v>
       </c>
       <c r="F33">
         <f t="shared" si="1"/>
-        <v>-0.27866959394364199</v>
+        <v>2.33915110109041</v>
       </c>
       <c r="G33" t="str">
         <f t="shared" si="2"/>
-        <v>-0.361018438089309-0.278669593943642i</v>
+        <v>0.218754879547233+2.33915110109041i</v>
       </c>
       <c r="H33" t="str">
         <f t="shared" si="3"/>
@@ -5819,19 +5821,19 @@
     </row>
     <row r="34" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D34" s="3" t="str">
-        <v>0.370253420413358-0.600830406711599i</v>
+        <v>1.25103059713347-0.124701380053342i</v>
       </c>
       <c r="E34">
         <f t="shared" si="0"/>
-        <v>0.37025342041335801</v>
+        <v>1.2510305971334701</v>
       </c>
       <c r="F34">
         <f t="shared" si="1"/>
-        <v>-0.60083040671159904</v>
+        <v>-0.124701380053342</v>
       </c>
       <c r="G34" t="str">
         <f t="shared" si="2"/>
-        <v>0.370253420413358-0.600830406711599i</v>
+        <v>1.25103059713347-0.124701380053342i</v>
       </c>
       <c r="H34" t="str">
         <f t="shared" si="3"/>
@@ -5840,19 +5842,19 @@
     </row>
     <row r="35" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D35" s="3" t="str">
-        <v>-1.18422333873192+0.371135101479369i</v>
+        <v>-0.400667457870699-0.130810019337373i</v>
       </c>
       <c r="E35">
         <f t="shared" si="0"/>
-        <v>-1.1842233387319201</v>
+        <v>-0.40066745787069902</v>
       </c>
       <c r="F35">
         <f t="shared" si="1"/>
-        <v>0.37113510147936901</v>
+        <v>-0.13081001933737299</v>
       </c>
       <c r="G35" t="str">
         <f t="shared" si="2"/>
-        <v>-1.18422333873192+0.371135101479369i</v>
+        <v>-0.400667457870699-0.130810019337373i</v>
       </c>
       <c r="H35" t="str">
         <f t="shared" si="3"/>
@@ -5861,19 +5863,19 @@
     </row>
     <row r="36" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D36" s="3" t="str">
-        <v>1.8949583230399+1.29688426027102i</v>
+        <v>-0.803783210982203+0.145144179948735i</v>
       </c>
       <c r="E36">
         <f t="shared" si="0"/>
-        <v>1.8949583230399001</v>
+        <v>-0.80378321098220296</v>
       </c>
       <c r="F36">
         <f t="shared" si="1"/>
-        <v>1.29688426027102</v>
+        <v>0.14514417994873499</v>
       </c>
       <c r="G36" t="str">
         <f t="shared" si="2"/>
-        <v>1.8949583230399+1.29688426027102i</v>
+        <v>-0.803783210982203+0.145144179948735i</v>
       </c>
       <c r="H36" t="str">
         <f t="shared" si="3"/>
@@ -5882,19 +5884,19 @@
     </row>
     <row r="37" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D37" s="3" t="str">
-        <v>-0.00303869713170772-0.335617731232341i</v>
+        <v>-0.56550909161372+0.570953705341257i</v>
       </c>
       <c r="E37">
         <f t="shared" si="0"/>
-        <v>-3.0386971317077202E-3</v>
+        <v>-0.56550909161371998</v>
       </c>
       <c r="F37">
         <f t="shared" si="1"/>
-        <v>-0.33561773123234101</v>
+        <v>0.570953705341257</v>
       </c>
       <c r="G37" t="str">
         <f t="shared" si="2"/>
-        <v>-0.00303869713170772-0.335617731232341i</v>
+        <v>-0.56550909161372+0.570953705341257i</v>
       </c>
       <c r="H37" t="str">
         <f t="shared" si="3"/>
@@ -5903,19 +5905,19 @@
     </row>
     <row r="38" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D38" s="3" t="str">
-        <v>0.155495896258558-0.606339781874627i</v>
+        <v>0.316320780000871+0.642460849449108i</v>
       </c>
       <c r="E38">
         <f t="shared" si="0"/>
-        <v>0.155495896258558</v>
+        <v>0.31632078000087099</v>
       </c>
       <c r="F38">
         <f t="shared" si="1"/>
-        <v>-0.606339781874627</v>
+        <v>0.64246084944910797</v>
       </c>
       <c r="G38" t="str">
         <f t="shared" si="2"/>
-        <v>0.155495896258558-0.606339781874627i</v>
+        <v>0.316320780000871+0.642460849449108i</v>
       </c>
       <c r="H38" t="str">
         <f t="shared" si="3"/>
@@ -5924,19 +5926,19 @@
     </row>
     <row r="39" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D39" s="3" t="str">
-        <v>-2.02390662792371+0.0979325554218866i</v>
+        <v>-0.100993414013384-0.431386066758254i</v>
       </c>
       <c r="E39">
         <f t="shared" si="0"/>
-        <v>-2.0239066279237101</v>
+        <v>-0.10099341401338401</v>
       </c>
       <c r="F39">
         <f t="shared" si="1"/>
-        <v>9.79325554218866E-2</v>
+        <v>-0.43138606675825403</v>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="2"/>
-        <v>-2.02390662792371+0.0979325554218866i</v>
+        <v>-0.100993414013384-0.431386066758254i</v>
       </c>
       <c r="H39" t="str">
         <f t="shared" si="3"/>
@@ -5945,19 +5947,19 @@
     </row>
     <row r="40" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D40" s="3" t="str">
-        <v>1.67366578164372-0.105001696314887i</v>
+        <v>-0.898305108230778-0.42022016292579i</v>
       </c>
       <c r="E40">
         <f t="shared" si="0"/>
-        <v>1.6736657816437199</v>
+        <v>-0.89830510823077803</v>
       </c>
       <c r="F40">
         <f t="shared" si="1"/>
-        <v>-0.105001696314887</v>
+        <v>-0.42022016292579001</v>
       </c>
       <c r="G40" t="str">
         <f t="shared" si="2"/>
-        <v>1.67366578164372-0.105001696314887i</v>
+        <v>-0.898305108230778-0.42022016292579i</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" si="3"/>
@@ -5966,19 +5968,19 @@
     </row>
     <row r="41" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D41" s="3" t="str">
-        <v>0.00654966850900085-0.843682511801686i</v>
+        <v>-0.348750371148591+1.18925850987545i</v>
       </c>
       <c r="E41">
         <f t="shared" si="0"/>
-        <v>6.54966850900085E-3</v>
+        <v>-0.34875037114859098</v>
       </c>
       <c r="F41">
         <f t="shared" si="1"/>
-        <v>-0.84368251180168596</v>
+        <v>1.18925850987545</v>
       </c>
       <c r="G41" t="str">
         <f t="shared" si="2"/>
-        <v>0.00654966850900085-0.843682511801686i</v>
+        <v>-0.348750371148591+1.18925850987545i</v>
       </c>
       <c r="H41" t="str">
         <f t="shared" si="3"/>
@@ -5987,19 +5989,19 @@
     </row>
     <row r="42" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D42" s="3" t="str">
-        <v>1.13657156578605-0.447668971271888i</v>
+        <v>0.492780645893229-0.754084024620817i</v>
       </c>
       <c r="E42">
         <f t="shared" si="0"/>
-        <v>1.13657156578605</v>
+        <v>0.49278064589322901</v>
       </c>
       <c r="F42">
         <f t="shared" si="1"/>
-        <v>-0.44766897127188798</v>
+        <v>-0.75408402462081703</v>
       </c>
       <c r="G42" t="str">
         <f t="shared" si="2"/>
-        <v>1.13657156578605-0.447668971271888i</v>
+        <v>0.492780645893229-0.754084024620817i</v>
       </c>
       <c r="H42" t="str">
         <f t="shared" si="3"/>
@@ -6008,19 +6010,19 @@
     </row>
     <row r="43" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D43" s="3" t="str">
-        <v>-0.681782023779965-0.418971017587804i</v>
+        <v>-0.0467505965477723+0.839726417457417i</v>
       </c>
       <c r="E43">
         <f t="shared" si="0"/>
-        <v>-0.681782023779965</v>
+        <v>-4.6750596547772298E-2</v>
       </c>
       <c r="F43">
         <f t="shared" si="1"/>
-        <v>-0.41897101758780397</v>
+        <v>0.83972641745741705</v>
       </c>
       <c r="G43" t="str">
         <f t="shared" si="2"/>
-        <v>-0.681782023779965-0.418971017587804i</v>
+        <v>-0.0467505965477723+0.839726417457417i</v>
       </c>
       <c r="H43" t="str">
         <f t="shared" si="3"/>
@@ -6029,19 +6031,19 @@
     </row>
     <row r="44" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D44" s="3" t="str">
-        <v>0.696763347521798+0.420840316867116i</v>
+        <v>-0.649459819158221-1.75788044363074i</v>
       </c>
       <c r="E44">
         <f t="shared" si="0"/>
-        <v>0.69676334752179803</v>
+        <v>-0.64945981915822104</v>
       </c>
       <c r="F44">
         <f t="shared" si="1"/>
-        <v>0.42084031686711598</v>
+        <v>-1.75788044363074</v>
       </c>
       <c r="G44" t="str">
         <f t="shared" si="2"/>
-        <v>0.696763347521798+0.420840316867116i</v>
+        <v>-0.649459819158221-1.75788044363074i</v>
       </c>
       <c r="H44" t="str">
         <f t="shared" si="3"/>
@@ -6050,19 +6052,19 @@
     </row>
     <row r="45" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D45" s="3" t="str">
-        <v>-0.777055185496489+0.0189652901457523i</v>
+        <v>0.55037564205409+0.45665046994817i</v>
       </c>
       <c r="E45">
         <f t="shared" si="0"/>
-        <v>-0.777055185496489</v>
+        <v>0.55037564205408995</v>
       </c>
       <c r="F45">
         <f t="shared" si="1"/>
-        <v>1.8965290145752298E-2</v>
+        <v>0.45665046994816999</v>
       </c>
       <c r="G45" t="str">
         <f t="shared" si="2"/>
-        <v>-0.777055185496489+0.0189652901457523i</v>
+        <v>0.55037564205409+0.45665046994817i</v>
       </c>
       <c r="H45" t="str">
         <f t="shared" si="3"/>
@@ -6071,19 +6073,19 @@
     </row>
     <row r="46" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D46" s="3" t="str">
-        <v>1.96685508123303+1.51951385600329i</v>
+        <v>-0.81395055801698+2.00298067158661i</v>
       </c>
       <c r="E46">
         <f t="shared" si="0"/>
-        <v>1.9668550812330301</v>
+        <v>-0.81395055801698002</v>
       </c>
       <c r="F46">
         <f t="shared" si="1"/>
-        <v>1.5195138560032899</v>
+        <v>2.0029806715866099</v>
       </c>
       <c r="G46" t="str">
         <f t="shared" si="2"/>
-        <v>1.96685508123303+1.51951385600329i</v>
+        <v>-0.81395055801698+2.00298067158661i</v>
       </c>
       <c r="H46" t="str">
         <f t="shared" si="3"/>
@@ -6092,19 +6094,19 @@
     </row>
     <row r="47" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D47" s="3" t="str">
-        <v>0.451865513185775-0.87405522431766i</v>
+        <v>-1.56495769807907+0.871233724962588i</v>
       </c>
       <c r="E47">
         <f t="shared" si="0"/>
-        <v>0.451865513185775</v>
+        <v>-1.56495769807907</v>
       </c>
       <c r="F47">
         <f t="shared" si="1"/>
-        <v>-0.87405522431766003</v>
+        <v>0.871233724962588</v>
       </c>
       <c r="G47" t="str">
         <f t="shared" si="2"/>
-        <v>0.451865513185775-0.87405522431766i</v>
+        <v>-1.56495769807907+0.871233724962588i</v>
       </c>
       <c r="H47" t="str">
         <f t="shared" si="3"/>
@@ -6113,19 +6115,19 @@
     </row>
     <row r="48" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D48" s="3" t="str">
-        <v>-0.900807372446822+0.931922474421746i</v>
+        <v>2.04150378604161-1.13898799261337i</v>
       </c>
       <c r="E48">
         <f t="shared" si="0"/>
-        <v>-0.90080737244682196</v>
+        <v>2.0415037860416101</v>
       </c>
       <c r="F48">
         <f t="shared" si="1"/>
-        <v>0.93192247442174603</v>
+        <v>-1.1389879926133699</v>
       </c>
       <c r="G48" t="str">
         <f t="shared" si="2"/>
-        <v>-0.900807372446822+0.931922474421746i</v>
+        <v>2.04150378604161-1.13898799261337i</v>
       </c>
       <c r="H48" t="str">
         <f t="shared" si="3"/>
@@ -6134,19 +6136,19 @@
     </row>
     <row r="49" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D49" s="3" t="str">
-        <v>-0.503351384388617+0.00135739741557999i</v>
+        <v>-0.536646404006027+1.0931064726989i</v>
       </c>
       <c r="E49">
         <f t="shared" si="0"/>
-        <v>-0.50335138438861704</v>
+        <v>-0.53664640400602703</v>
       </c>
       <c r="F49">
         <f t="shared" si="1"/>
-        <v>1.3573974155799899E-3</v>
+        <v>1.0931064726988999</v>
       </c>
       <c r="G49" t="str">
         <f t="shared" si="2"/>
-        <v>-0.503351384388617+0.00135739741557999i</v>
+        <v>-0.536646404006027+1.0931064726989i</v>
       </c>
       <c r="H49" t="str">
         <f t="shared" si="3"/>
@@ -6155,19 +6157,19 @@
     </row>
     <row r="50" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D50" s="3" t="str">
-        <v>-1.18233513246494+2.58765536239327i</v>
+        <v>-0.606946173065575+1.01141606118781i</v>
       </c>
       <c r="E50">
         <f t="shared" si="0"/>
-        <v>-1.18233513246494</v>
+        <v>-0.60694617306557497</v>
       </c>
       <c r="F50">
         <f t="shared" si="1"/>
-        <v>2.5876553623932699</v>
+        <v>1.01141606118781</v>
       </c>
       <c r="G50" t="str">
         <f t="shared" si="2"/>
-        <v>-1.18233513246494+2.58765536239327i</v>
+        <v>-0.606946173065575+1.01141606118781i</v>
       </c>
       <c r="H50" t="str">
         <f t="shared" si="3"/>
@@ -6176,19 +6178,19 @@
     </row>
     <row r="51" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D51" s="3" t="str">
-        <v>-1.27836036427547+0.314707353786093i</v>
+        <v>0.0174038079986121+0.343133267156729i</v>
       </c>
       <c r="E51">
         <f t="shared" si="0"/>
-        <v>-1.27836036427547</v>
+        <v>1.74038079986121E-2</v>
       </c>
       <c r="F51">
         <f t="shared" si="1"/>
-        <v>0.31470735378609299</v>
+        <v>0.34313326715672898</v>
       </c>
       <c r="G51" t="str">
         <f t="shared" si="2"/>
-        <v>-1.27836036427547+0.314707353786093i</v>
+        <v>0.0174038079986121+0.343133267156729i</v>
       </c>
       <c r="H51" t="str">
         <f t="shared" si="3"/>
@@ -6197,19 +6199,19 @@
     </row>
     <row r="52" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D52" s="3" t="str">
-        <v>-0.110878996272388+1.18906553386974i</v>
+        <v>0.755109810700653+0.896827638170199i</v>
       </c>
       <c r="E52">
         <f t="shared" si="0"/>
-        <v>-0.11087899627238799</v>
+        <v>0.75510981070065297</v>
       </c>
       <c r="F52">
         <f t="shared" si="1"/>
-        <v>1.18906553386974</v>
+        <v>0.89682763817019895</v>
       </c>
       <c r="G52" t="str">
         <f t="shared" si="2"/>
-        <v>-0.110878996272388+1.18906553386974i</v>
+        <v>0.755109810700653+0.896827638170199i</v>
       </c>
       <c r="H52" t="str">
         <f t="shared" si="3"/>
@@ -6218,19 +6220,19 @@
     </row>
     <row r="53" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D53" s="3" t="str">
-        <v>0.541260311622223+0.593807747669956i</v>
+        <v>2.19966928958898-0.18392976003785i</v>
       </c>
       <c r="E53">
         <f t="shared" si="0"/>
-        <v>0.54126031162222299</v>
+        <v>2.19966928958898</v>
       </c>
       <c r="F53">
         <f t="shared" si="1"/>
-        <v>0.59380774766995603</v>
+        <v>-0.18392976003785</v>
       </c>
       <c r="G53" t="str">
         <f t="shared" si="2"/>
-        <v>0.541260311622223+0.593807747669956i</v>
+        <v>2.19966928958898-0.18392976003785i</v>
       </c>
       <c r="H53" t="str">
         <f t="shared" si="3"/>
@@ -6239,19 +6241,19 @@
     </row>
     <row r="54" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D54" s="3" t="str">
-        <v>-0.170967089809201+0.263708864275274i</v>
+        <v>-1.36868753249761-0.249602978107702i</v>
       </c>
       <c r="E54">
         <f t="shared" si="0"/>
-        <v>-0.170967089809201</v>
+        <v>-1.36868753249761</v>
       </c>
       <c r="F54">
         <f t="shared" si="1"/>
-        <v>0.26370886427527401</v>
+        <v>-0.24960297810770199</v>
       </c>
       <c r="G54" t="str">
         <f t="shared" si="2"/>
-        <v>-0.170967089809201+0.263708864275274i</v>
+        <v>-1.36868753249761-0.249602978107702i</v>
       </c>
       <c r="H54" t="str">
         <f t="shared" si="3"/>
@@ -6260,19 +6262,19 @@
     </row>
     <row r="55" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D55" s="3" t="str">
-        <v>-1.96579077078331+1.04348629265086i</v>
+        <v>-1.980185490143-0.379604561098807i</v>
       </c>
       <c r="E55">
         <f t="shared" si="0"/>
-        <v>-1.96579077078331</v>
+        <v>-1.980185490143</v>
       </c>
       <c r="F55">
         <f t="shared" si="1"/>
-        <v>1.0434862926508599</v>
+        <v>-0.37960456109880703</v>
       </c>
       <c r="G55" t="str">
         <f t="shared" si="2"/>
-        <v>-1.96579077078331+1.04348629265086i</v>
+        <v>-1.980185490143-0.379604561098807i</v>
       </c>
       <c r="H55" t="str">
         <f t="shared" si="3"/>
@@ -6281,19 +6283,19 @@
     </row>
     <row r="56" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D56" s="3" t="str">
-        <v>-2.63780250994699+0.556332556616364i</v>
+        <v>1.84346933647334-1.66115181338913i</v>
       </c>
       <c r="E56">
         <f t="shared" si="0"/>
-        <v>-2.6378025099469902</v>
+        <v>1.8434693364733401</v>
       </c>
       <c r="F56">
         <f t="shared" si="1"/>
-        <v>0.55633255661636405</v>
+        <v>-1.6611518133891301</v>
       </c>
       <c r="G56" t="str">
         <f t="shared" si="2"/>
-        <v>-2.63780250994699+0.556332556616364i</v>
+        <v>1.84346933647334-1.66115181338913i</v>
       </c>
       <c r="H56" t="str">
         <f t="shared" si="3"/>
@@ -6302,19 +6304,19 @@
     </row>
     <row r="57" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D57" s="3" t="str">
-        <v>-0.378715645802191+0.0965329816611683i</v>
+        <v>0.562082688910423+1.00122996332087i</v>
       </c>
       <c r="E57">
         <f t="shared" si="0"/>
-        <v>-0.37871564580219103</v>
+        <v>0.56208268891042301</v>
       </c>
       <c r="F57">
         <f t="shared" si="1"/>
-        <v>9.6532981661168304E-2</v>
+        <v>1.0012299633208701</v>
       </c>
       <c r="G57" t="str">
         <f t="shared" si="2"/>
-        <v>-0.378715645802191+0.0965329816611683i</v>
+        <v>0.562082688910423+1.00122996332087i</v>
       </c>
       <c r="H57" t="str">
         <f t="shared" si="3"/>
@@ -6323,19 +6325,19 @@
     </row>
     <row r="58" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D58" s="3" t="str">
-        <v>-0.588225767797975-0.888921227226115i</v>
+        <v>0.378072024438642-0.399662290390968i</v>
       </c>
       <c r="E58">
         <f t="shared" si="0"/>
-        <v>-0.58822576779797497</v>
+        <v>0.37807202443864202</v>
       </c>
       <c r="F58">
         <f t="shared" si="1"/>
-        <v>-0.888921227226115</v>
+        <v>-0.39966229039096801</v>
       </c>
       <c r="G58" t="str">
         <f t="shared" si="2"/>
-        <v>-0.588225767797975-0.888921227226115i</v>
+        <v>0.378072024438642-0.399662290390968i</v>
       </c>
       <c r="H58" t="str">
         <f t="shared" si="3"/>
@@ -6344,19 +6346,19 @@
     </row>
     <row r="59" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D59" s="3" t="str">
-        <v>0.0150277404213967-1.28721089132595i</v>
+        <v>-0.565139333855761-0.389826463776988i</v>
       </c>
       <c r="E59">
         <f t="shared" si="0"/>
-        <v>1.50277404213967E-2</v>
+        <v>-0.56513933385576098</v>
       </c>
       <c r="F59">
         <f t="shared" si="1"/>
-        <v>-1.2872108913259499</v>
+        <v>-0.38982646377698799</v>
       </c>
       <c r="G59" t="str">
         <f t="shared" si="2"/>
-        <v>0.0150277404213967-1.28721089132595i</v>
+        <v>-0.565139333855761-0.389826463776988i</v>
       </c>
       <c r="H59" t="str">
         <f t="shared" si="3"/>
@@ -6365,19 +6367,19 @@
     </row>
     <row r="60" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D60" s="3" t="str">
-        <v>0.0421550902573912+0.0425245334298609i</v>
+        <v>-0.061858855909151+0.373029898673202i</v>
       </c>
       <c r="E60">
         <f t="shared" si="0"/>
-        <v>4.2155090257391198E-2</v>
+        <v>-6.1858855909151002E-2</v>
       </c>
       <c r="F60">
         <f t="shared" si="1"/>
-        <v>4.25245334298609E-2</v>
+        <v>0.37302989867320202</v>
       </c>
       <c r="G60" t="str">
         <f t="shared" si="2"/>
-        <v>0.0421550902573912+0.0425245334298609i</v>
+        <v>-0.061858855909151+0.373029898673202i</v>
       </c>
       <c r="H60" t="str">
         <f t="shared" si="3"/>
@@ -6386,19 +6388,19 @@
     </row>
     <row r="61" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D61" s="3" t="str">
-        <v>0.552859693340389+0.0500810468404363i</v>
+        <v>-0.0377606018972269+2.30977877764508i</v>
       </c>
       <c r="E61">
         <f t="shared" si="0"/>
-        <v>0.55285969334038898</v>
+        <v>-3.7760601897226902E-2</v>
       </c>
       <c r="F61">
         <f t="shared" si="1"/>
-        <v>5.0081046840436301E-2</v>
+        <v>2.30977877764508</v>
       </c>
       <c r="G61" t="str">
         <f t="shared" si="2"/>
-        <v>0.552859693340389+0.0500810468404363i</v>
+        <v>-0.0377606018972269+2.30977877764508i</v>
       </c>
       <c r="H61" t="str">
         <f t="shared" si="3"/>
@@ -6407,19 +6409,19 @@
     </row>
     <row r="62" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D62" s="3" t="str">
-        <v>-0.589484502046212+0.0340569409158721i</v>
+        <v>0.902000915738111+0.307015940773105i</v>
       </c>
       <c r="E62">
         <f t="shared" si="0"/>
-        <v>-0.58948450204621206</v>
+        <v>0.90200091573811103</v>
       </c>
       <c r="F62">
         <f t="shared" si="1"/>
-        <v>3.4056940915872101E-2</v>
+        <v>0.30701594077310501</v>
       </c>
       <c r="G62" t="str">
         <f t="shared" si="2"/>
-        <v>-0.589484502046212+0.0340569409158721i</v>
+        <v>0.902000915738111+0.307015940773105i</v>
       </c>
       <c r="H62" t="str">
         <f t="shared" si="3"/>
@@ -6428,19 +6430,19 @@
     </row>
     <row r="63" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D63" s="3" t="str">
-        <v>-0.109522851597525-0.383090597592882i</v>
+        <v>0.0850070859395772-0.209678279945316i</v>
       </c>
       <c r="E63">
         <f t="shared" si="0"/>
-        <v>-0.10952285159752501</v>
+        <v>8.5007085939577204E-2</v>
       </c>
       <c r="F63">
         <f t="shared" si="1"/>
-        <v>-0.383090597592882</v>
+        <v>-0.20967827994531599</v>
       </c>
       <c r="G63" t="str">
         <f t="shared" si="2"/>
-        <v>-0.109522851597525-0.383090597592882i</v>
+        <v>0.0850070859395772-0.209678279945316i</v>
       </c>
       <c r="H63" t="str">
         <f t="shared" si="3"/>
@@ -6449,19 +6451,19 @@
     </row>
     <row r="64" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D64" s="3" t="str">
-        <v>0.928626599814376+0.561081782382289i</v>
+        <v>-1.09909059361063-0.437441864700752i</v>
       </c>
       <c r="E64">
         <f t="shared" si="0"/>
-        <v>0.92862659981437601</v>
+        <v>-1.0990905936106301</v>
       </c>
       <c r="F64">
         <f t="shared" si="1"/>
-        <v>0.56108178238228901</v>
+        <v>-0.43744186470075203</v>
       </c>
       <c r="G64" t="str">
         <f t="shared" si="2"/>
-        <v>0.928626599814376+0.561081782382289i</v>
+        <v>-1.09909059361063-0.437441864700752i</v>
       </c>
       <c r="H64" t="str">
         <f t="shared" si="3"/>
@@ -6470,19 +6472,19 @@
     </row>
     <row r="65" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D65" s="3" t="str">
-        <v>-0.39133239956942-1.00747992683127i</v>
+        <v>-0.806754583059857-1.17959248287074i</v>
       </c>
       <c r="E65">
         <f t="shared" si="0"/>
-        <v>-0.39133239956942001</v>
+        <v>-0.80675458305985703</v>
       </c>
       <c r="F65">
         <f t="shared" si="1"/>
-        <v>-1.00747992683127</v>
+        <v>-1.17959248287074</v>
       </c>
       <c r="G65" t="str">
         <f t="shared" si="2"/>
-        <v>-0.39133239956942-1.00747992683127i</v>
+        <v>-0.806754583059857-1.17959248287074i</v>
       </c>
       <c r="H65" t="str">
         <f t="shared" si="3"/>
@@ -6491,19 +6493,19 @@
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D66" s="3" t="str">
-        <v>0.824428305678373+0.674907785802673i</v>
+        <v>-0.807887017866844-0.341984893586169i</v>
       </c>
       <c r="E66">
         <f t="shared" si="0"/>
-        <v>0.824428305678373</v>
+        <v>-0.80788701786684403</v>
       </c>
       <c r="F66">
         <f t="shared" si="1"/>
-        <v>0.67490778580267297</v>
+        <v>-0.34198489358616901</v>
       </c>
       <c r="G66" t="str">
         <f t="shared" si="2"/>
-        <v>0.824428305678373+0.674907785802673i</v>
+        <v>-0.807887017866844-0.341984893586169i</v>
       </c>
       <c r="H66" t="str">
         <f t="shared" si="3"/>
@@ -6512,19 +6514,19 @@
     </row>
     <row r="67" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D67" s="3" t="str">
-        <v>-0.611459720382313+0.453464326214954i</v>
+        <v>-0.367354616179967-0.936415667980221i</v>
       </c>
       <c r="E67">
         <f t="shared" si="0"/>
-        <v>-0.611459720382313</v>
+        <v>-0.36735461617996701</v>
       </c>
       <c r="F67">
         <f t="shared" si="1"/>
-        <v>0.45346432621495403</v>
+        <v>-0.93641566798022102</v>
       </c>
       <c r="G67" t="str">
         <f t="shared" si="2"/>
-        <v>-0.611459720382313+0.453464326214954i</v>
+        <v>-0.367354616179967-0.936415667980221i</v>
       </c>
       <c r="H67" t="str">
         <f t="shared" si="3"/>
@@ -6533,19 +6535,19 @@
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D68" s="3" t="str">
-        <v>-1.27776512040646-1.98552190105661i</v>
+        <v>0.361956583326583-0.753219885363427i</v>
       </c>
       <c r="E68">
         <f t="shared" ref="E68:E102" si="4">IMREAL(D68)</f>
-        <v>-1.27776512040646</v>
+        <v>0.36195658332658298</v>
       </c>
       <c r="F68">
         <f t="shared" ref="F68:F102" si="5">IMAGINARY(D68)</f>
-        <v>-1.9855219010566101</v>
+        <v>-0.75321988536342699</v>
       </c>
       <c r="G68" t="str">
         <f t="shared" ref="G68:G102" si="6">COMPLEX(ROUND(E68, $G$2), ROUND(F68, $G$2))</f>
-        <v>-1.27776512040646-1.98552190105661i</v>
+        <v>0.361956583326583-0.753219885363427i</v>
       </c>
       <c r="H68" t="str">
         <f t="shared" ref="H68:H102" si="7">IF(G68=D68, "OK", "FAIL")</f>
@@ -6554,19 +6556,19 @@
     </row>
     <row r="69" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D69" s="3" t="str">
-        <v>1.1086139831762-0.362823490716077i</v>
+        <v>-1.72391277448523+0.275333623294372i</v>
       </c>
       <c r="E69">
         <f t="shared" si="4"/>
-        <v>1.1086139831762001</v>
+        <v>-1.7239127744852301</v>
       </c>
       <c r="F69">
         <f t="shared" si="5"/>
-        <v>-0.362823490716077</v>
+        <v>0.275333623294372</v>
       </c>
       <c r="G69" t="str">
         <f t="shared" si="6"/>
-        <v>1.1086139831762-0.362823490716077i</v>
+        <v>-1.72391277448523+0.275333623294372i</v>
       </c>
       <c r="H69" t="str">
         <f t="shared" si="7"/>
@@ -6575,19 +6577,19 @@
     </row>
     <row r="70" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D70" s="3" t="str">
-        <v>-1.19045635191436-1.17615735402908i</v>
+        <v>0.369417102142978+0.860136800618968i</v>
       </c>
       <c r="E70">
         <f t="shared" si="4"/>
-        <v>-1.1904563519143601</v>
+        <v>0.36941710214297802</v>
       </c>
       <c r="F70">
         <f t="shared" si="5"/>
-        <v>-1.1761573540290799</v>
+        <v>0.86013680061896802</v>
       </c>
       <c r="G70" t="str">
         <f t="shared" si="6"/>
-        <v>-1.19045635191436-1.17615735402908i</v>
+        <v>0.369417102142978+0.860136800618968i</v>
       </c>
       <c r="H70" t="str">
         <f t="shared" si="7"/>
@@ -6596,19 +6598,19 @@
     </row>
     <row r="71" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D71" s="3" t="str">
-        <v>-1.07353148779264-1.215992027275i</v>
+        <v>0.563722395410846-0.0318270213899254i</v>
       </c>
       <c r="E71">
         <f t="shared" si="4"/>
-        <v>-1.0735314877926401</v>
+        <v>0.56372239541084601</v>
       </c>
       <c r="F71">
         <f t="shared" si="5"/>
-        <v>-1.215992027275</v>
+        <v>-3.1827021389925401E-2</v>
       </c>
       <c r="G71" t="str">
         <f t="shared" si="6"/>
-        <v>-1.07353148779264-1.215992027275i</v>
+        <v>0.563722395410846-0.0318270213899254i</v>
       </c>
       <c r="H71" t="str">
         <f t="shared" si="7"/>
@@ -6617,19 +6619,19 @@
     </row>
     <row r="72" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D72" s="3" t="str">
-        <v>2.63162245602807-3.29925364964694i</v>
+        <v>0.15751211431459+1.35946233138978i</v>
       </c>
       <c r="E72">
         <f t="shared" si="4"/>
-        <v>2.6316224560280701</v>
+        <v>0.15751211431459</v>
       </c>
       <c r="F72">
         <f t="shared" si="5"/>
-        <v>-3.29925364964694</v>
+        <v>1.35946233138978</v>
       </c>
       <c r="G72" t="str">
         <f t="shared" si="6"/>
-        <v>2.63162245602807-3.29925364964694i</v>
+        <v>0.15751211431459+1.35946233138978i</v>
       </c>
       <c r="H72" t="str">
         <f t="shared" si="7"/>
@@ -6638,19 +6640,19 @@
     </row>
     <row r="73" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D73" s="3" t="str">
-        <v>-1.20970803185388+0.318628992929885i</v>
+        <v>0.178356603654718+1.48323848163915i</v>
       </c>
       <c r="E73">
         <f t="shared" si="4"/>
-        <v>-1.20970803185388</v>
+        <v>0.178356603654718</v>
       </c>
       <c r="F73">
         <f t="shared" si="5"/>
-        <v>0.318628992929885</v>
+        <v>1.48323848163915</v>
       </c>
       <c r="G73" t="str">
         <f t="shared" si="6"/>
-        <v>-1.20970803185388+0.318628992929885i</v>
+        <v>0.178356603654718+1.48323848163915i</v>
       </c>
       <c r="H73" t="str">
         <f t="shared" si="7"/>
@@ -6659,19 +6661,19 @@
     </row>
     <row r="74" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D74" s="3" t="str">
-        <v>0.0824234840054471+0.137627871839614i</v>
+        <v>-0.37926725501036+1.91749880170607i</v>
       </c>
       <c r="E74">
         <f t="shared" si="4"/>
-        <v>8.2423484005447106E-2</v>
+        <v>-0.37926725501036002</v>
       </c>
       <c r="F74">
         <f t="shared" si="5"/>
-        <v>0.137627871839614</v>
+        <v>1.9174988017060699</v>
       </c>
       <c r="G74" t="str">
         <f t="shared" si="6"/>
-        <v>0.0824234840054471+0.137627871839614i</v>
+        <v>-0.37926725501036+1.91749880170607i</v>
       </c>
       <c r="H74" t="str">
         <f t="shared" si="7"/>
@@ -6680,19 +6682,19 @@
     </row>
     <row r="75" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D75" s="3" t="str">
-        <v>-1.11238765765698-0.977904073578398i</v>
+        <v>0.499383374637175-0.989782031871395i</v>
       </c>
       <c r="E75">
         <f t="shared" si="4"/>
-        <v>-1.11238765765698</v>
+        <v>0.49938337463717503</v>
       </c>
       <c r="F75">
         <f t="shared" si="5"/>
-        <v>-0.97790407357839804</v>
+        <v>-0.98978203187139502</v>
       </c>
       <c r="G75" t="str">
         <f t="shared" si="6"/>
-        <v>-1.11238765765698-0.977904073578398i</v>
+        <v>0.499383374637175-0.989782031871395i</v>
       </c>
       <c r="H75" t="str">
         <f t="shared" si="7"/>
@@ -6701,19 +6703,19 @@
     </row>
     <row r="76" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D76" s="3" t="str">
-        <v>-0.0501224126189895+1.2408949940575i</v>
+        <v>0.0347709123411174+0.0348234338344951i</v>
       </c>
       <c r="E76">
         <f t="shared" si="4"/>
-        <v>-5.0122412618989497E-2</v>
+        <v>3.4770912341117399E-2</v>
       </c>
       <c r="F76">
         <f t="shared" si="5"/>
-        <v>1.2408949940575</v>
+        <v>3.4823433834495099E-2</v>
       </c>
       <c r="G76" t="str">
         <f t="shared" si="6"/>
-        <v>-0.0501224126189895+1.2408949940575i</v>
+        <v>0.0347709123411174+0.0348234338344951i</v>
       </c>
       <c r="H76" t="str">
         <f t="shared" si="7"/>
@@ -6722,19 +6724,19 @@
     </row>
     <row r="77" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D77" s="3" t="str">
-        <v>-0.0690165280466283-0.392027215630862i</v>
+        <v>-0.104371144798576-0.58746849453525i</v>
       </c>
       <c r="E77">
         <f t="shared" si="4"/>
-        <v>-6.9016528046628306E-2</v>
+        <v>-0.104371144798576</v>
       </c>
       <c r="F77">
         <f t="shared" si="5"/>
-        <v>-0.39202721563086201</v>
+        <v>-0.58746849453524996</v>
       </c>
       <c r="G77" t="str">
         <f t="shared" si="6"/>
-        <v>-0.0690165280466283-0.392027215630862i</v>
+        <v>-0.104371144798576-0.58746849453525i</v>
       </c>
       <c r="H77" t="str">
         <f t="shared" si="7"/>
@@ -6743,19 +6745,19 @@
     </row>
     <row r="78" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D78" s="3" t="str">
-        <v>-1.63039329720255-1.38787101104131i</v>
+        <v>-0.66049288735372+1.55733338823431i</v>
       </c>
       <c r="E78">
         <f t="shared" si="4"/>
-        <v>-1.6303932972025501</v>
+        <v>-0.66049288735372003</v>
       </c>
       <c r="F78">
         <f t="shared" si="5"/>
-        <v>-1.3878710110413099</v>
+        <v>1.5573333882343099</v>
       </c>
       <c r="G78" t="str">
         <f t="shared" si="6"/>
-        <v>-1.63039329720255-1.38787101104131i</v>
+        <v>-0.66049288735372+1.55733338823431i</v>
       </c>
       <c r="H78" t="str">
         <f t="shared" si="7"/>
@@ -6764,19 +6766,19 @@
     </row>
     <row r="79" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D79" s="3" t="str">
-        <v>0.103294506484819-0.136500082047739i</v>
+        <v>-0.489713705338264-0.00999533866515553i</v>
       </c>
       <c r="E79">
         <f t="shared" si="4"/>
-        <v>0.103294506484819</v>
+        <v>-0.48971370533826403</v>
       </c>
       <c r="F79">
         <f t="shared" si="5"/>
-        <v>-0.136500082047739</v>
+        <v>-9.9953386651555308E-3</v>
       </c>
       <c r="G79" t="str">
         <f t="shared" si="6"/>
-        <v>0.103294506484819-0.136500082047739i</v>
+        <v>-0.489713705338264-0.00999533866515553i</v>
       </c>
       <c r="H79" t="str">
         <f t="shared" si="7"/>
@@ -6785,19 +6787,19 @@
     </row>
     <row r="80" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D80" s="3" t="str">
-        <v>-0.719881620683433+1.22001243711018i</v>
+        <v>-0.362815070608996+0.232439713495332i</v>
       </c>
       <c r="E80">
         <f t="shared" si="4"/>
-        <v>-0.71988162068343298</v>
+        <v>-0.36281507060899598</v>
       </c>
       <c r="F80">
         <f t="shared" si="5"/>
-        <v>1.2200124371101799</v>
+        <v>0.23243971349533199</v>
       </c>
       <c r="G80" t="str">
         <f t="shared" si="6"/>
-        <v>-0.719881620683433+1.22001243711018i</v>
+        <v>-0.362815070608996+0.232439713495332i</v>
       </c>
       <c r="H80" t="str">
         <f t="shared" si="7"/>
@@ -6806,19 +6808,19 @@
     </row>
     <row r="81" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D81" s="3" t="str">
-        <v>0.00377226219101953+0.626949939550793i</v>
+        <v>-0.933681255640022+0.885546266526287i</v>
       </c>
       <c r="E81">
         <f t="shared" si="4"/>
-        <v>3.7722621910195298E-3</v>
+        <v>-0.93368125564002202</v>
       </c>
       <c r="F81">
         <f t="shared" si="5"/>
-        <v>0.62694993955079303</v>
+        <v>0.88554626652628698</v>
       </c>
       <c r="G81" t="str">
         <f t="shared" si="6"/>
-        <v>0.00377226219101953+0.626949939550793i</v>
+        <v>-0.933681255640022+0.885546266526287i</v>
       </c>
       <c r="H81" t="str">
         <f t="shared" si="7"/>
@@ -6827,19 +6829,19 @@
     </row>
     <row r="82" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D82" s="3" t="str">
-        <v>-0.0358810836308664+1.16905724372672i</v>
+        <v>-0.276225803286021+1.1272881030225i</v>
       </c>
       <c r="E82">
         <f t="shared" si="4"/>
-        <v>-3.5881083630866402E-2</v>
+        <v>-0.27622580328602098</v>
       </c>
       <c r="F82">
         <f t="shared" si="5"/>
-        <v>1.1690572437267199</v>
+        <v>1.1272881030224999</v>
       </c>
       <c r="G82" t="str">
         <f t="shared" si="6"/>
-        <v>-0.0358810836308664+1.16905724372672i</v>
+        <v>-0.276225803286021+1.1272881030225i</v>
       </c>
       <c r="H82" t="str">
         <f t="shared" si="7"/>
@@ -6848,19 +6850,19 @@
     </row>
     <row r="83" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D83" s="3" t="str">
-        <v>0.1841762913402-0.220080418278264i</v>
+        <v>-1.32259514091931+0.509225495520957i</v>
       </c>
       <c r="E83">
         <f t="shared" si="4"/>
-        <v>0.1841762913402</v>
+        <v>-1.32259514091931</v>
       </c>
       <c r="F83">
         <f t="shared" si="5"/>
-        <v>-0.220080418278264</v>
+        <v>0.50922549552095697</v>
       </c>
       <c r="G83" t="str">
         <f t="shared" si="6"/>
-        <v>0.1841762913402-0.220080418278264i</v>
+        <v>-1.32259514091931+0.509225495520957i</v>
       </c>
       <c r="H83" t="str">
         <f t="shared" si="7"/>
@@ -6869,19 +6871,19 @@
     </row>
     <row r="84" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D84" s="3" t="str">
-        <v>-0.59594883406532+0.729211830717087i</v>
+        <v>0.66286847263945+0.715363637620017i</v>
       </c>
       <c r="E84">
         <f t="shared" si="4"/>
-        <v>-0.59594883406531995</v>
+        <v>0.66286847263945003</v>
       </c>
       <c r="F84">
         <f t="shared" si="5"/>
-        <v>0.72921183071708695</v>
+        <v>0.71536363762001698</v>
       </c>
       <c r="G84" t="str">
         <f t="shared" si="6"/>
-        <v>-0.59594883406532+0.729211830717087i</v>
+        <v>0.66286847263945+0.715363637620017i</v>
       </c>
       <c r="H84" t="str">
         <f t="shared" si="7"/>
@@ -6890,19 +6892,19 @@
     </row>
     <row r="85" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D85" s="3" t="str">
-        <v>0.265168241030976-1.18514800641547i</v>
+        <v>-1.75881995282656+1.20145721138734i</v>
       </c>
       <c r="E85">
         <f t="shared" si="4"/>
-        <v>0.26516824103097603</v>
+        <v>-1.75881995282656</v>
       </c>
       <c r="F85">
         <f t="shared" si="5"/>
-        <v>-1.18514800641547</v>
+        <v>1.2014572113873401</v>
       </c>
       <c r="G85" t="str">
         <f t="shared" si="6"/>
-        <v>0.265168241030976-1.18514800641547i</v>
+        <v>-1.75881995282656+1.20145721138734i</v>
       </c>
       <c r="H85" t="str">
         <f t="shared" si="7"/>
@@ -6911,19 +6913,19 @@
     </row>
     <row r="86" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D86" s="3" t="str">
-        <v>0.847221208348836+0.750820321753472i</v>
+        <v>0.706188208032826-1.44268707129901i</v>
       </c>
       <c r="E86">
         <f t="shared" si="4"/>
-        <v>0.84722120834883596</v>
+        <v>0.706188208032826</v>
       </c>
       <c r="F86">
         <f t="shared" si="5"/>
-        <v>0.75082032175347202</v>
+        <v>-1.4426870712990101</v>
       </c>
       <c r="G86" t="str">
         <f t="shared" si="6"/>
-        <v>0.847221208348836+0.750820321753472i</v>
+        <v>0.706188208032826-1.44268707129901i</v>
       </c>
       <c r="H86" t="str">
         <f t="shared" si="7"/>
@@ -6932,19 +6934,19 @@
     </row>
     <row r="87" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D87" s="3" t="str">
-        <v>-0.565538895111685-0.135169963754507i</v>
+        <v>-0.435660157518374+0.711565946919547i</v>
       </c>
       <c r="E87">
         <f t="shared" si="4"/>
-        <v>-0.56553889511168498</v>
+        <v>-0.435660157518374</v>
       </c>
       <c r="F87">
         <f t="shared" si="5"/>
-        <v>-0.13516996375450699</v>
+        <v>0.711565946919547</v>
       </c>
       <c r="G87" t="str">
         <f t="shared" si="6"/>
-        <v>-0.565538895111685-0.135169963754507i</v>
+        <v>-0.435660157518374+0.711565946919547i</v>
       </c>
       <c r="H87" t="str">
         <f t="shared" si="7"/>
@@ -6953,19 +6955,19 @@
     </row>
     <row r="88" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D88" s="3" t="str">
-        <v>-0.699369005493585-0.071221262739605i</v>
+        <v>-0.4455515154958+0.685437425404727i</v>
       </c>
       <c r="E88">
         <f t="shared" si="4"/>
-        <v>-0.69936900549358505</v>
+        <v>-0.44555151549580002</v>
       </c>
       <c r="F88">
         <f t="shared" si="5"/>
-        <v>-7.1221262739604996E-2</v>
+        <v>0.68543742540472696</v>
       </c>
       <c r="G88" t="str">
         <f t="shared" si="6"/>
-        <v>-0.699369005493585-0.071221262739605i</v>
+        <v>-0.4455515154958+0.685437425404727i</v>
       </c>
       <c r="H88" t="str">
         <f t="shared" si="7"/>
@@ -6974,19 +6976,19 @@
     </row>
     <row r="89" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D89" s="3" t="str">
-        <v>0.454167031918698+0.768620895123811i</v>
+        <v>0.37480904019522-0.309992009036549i</v>
       </c>
       <c r="E89">
         <f t="shared" si="4"/>
-        <v>0.45416703191869801</v>
+        <v>0.37480904019521999</v>
       </c>
       <c r="F89">
         <f t="shared" si="5"/>
-        <v>0.76862089512381104</v>
+        <v>-0.309992009036549</v>
       </c>
       <c r="G89" t="str">
         <f t="shared" si="6"/>
-        <v>0.454167031918698+0.768620895123811i</v>
+        <v>0.37480904019522-0.309992009036549i</v>
       </c>
       <c r="H89" t="str">
         <f t="shared" si="7"/>
@@ -6995,19 +6997,19 @@
     </row>
     <row r="90" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D90" s="3" t="str">
-        <v>-0.418706563760354-0.108010344175216i</v>
+        <v>-1.56923072702817+0.874664086268642i</v>
       </c>
       <c r="E90">
         <f t="shared" si="4"/>
-        <v>-0.41870656376035398</v>
+        <v>-1.56923072702817</v>
       </c>
       <c r="F90">
         <f t="shared" si="5"/>
-        <v>-0.108010344175216</v>
+        <v>0.874664086268642</v>
       </c>
       <c r="G90" t="str">
         <f t="shared" si="6"/>
-        <v>-0.418706563760354-0.108010344175216i</v>
+        <v>-1.56923072702817+0.874664086268642i</v>
       </c>
       <c r="H90" t="str">
         <f t="shared" si="7"/>
@@ -7016,19 +7018,19 @@
     </row>
     <row r="91" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D91" s="3" t="str">
-        <v>0.364338693371595-0.17365340812418i</v>
+        <v>-0.77716536254421+0.450593123614705i</v>
       </c>
       <c r="E91">
         <f t="shared" si="4"/>
-        <v>0.36433869337159502</v>
+        <v>-0.77716536254420998</v>
       </c>
       <c r="F91">
         <f t="shared" si="5"/>
-        <v>-0.17365340812418001</v>
+        <v>0.45059312361470499</v>
       </c>
       <c r="G91" t="str">
         <f t="shared" si="6"/>
-        <v>0.364338693371595-0.17365340812418i</v>
+        <v>-0.77716536254421+0.450593123614705i</v>
       </c>
       <c r="H91" t="str">
         <f t="shared" si="7"/>
@@ -7037,19 +7039,19 @@
     </row>
     <row r="92" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D92" s="3" t="str">
-        <v>-0.166324067351185-1.13313816754947i</v>
+        <v>-0.843555800635632-0.241567658222894i</v>
       </c>
       <c r="E92">
         <f t="shared" si="4"/>
-        <v>-0.16632406735118499</v>
+        <v>-0.84355580063563196</v>
       </c>
       <c r="F92">
         <f t="shared" si="5"/>
-        <v>-1.1331381675494701</v>
+        <v>-0.241567658222894</v>
       </c>
       <c r="G92" t="str">
         <f t="shared" si="6"/>
-        <v>-0.166324067351185-1.13313816754947i</v>
+        <v>-0.843555800635632-0.241567658222894i</v>
       </c>
       <c r="H92" t="str">
         <f t="shared" si="7"/>
@@ -7058,19 +7060,19 @@
     </row>
     <row r="93" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D93" s="3" t="str">
-        <v>0.490554562992942+1.34186661179069i</v>
+        <v>-3.60230735361442+1.06209962834421i</v>
       </c>
       <c r="E93">
         <f t="shared" si="4"/>
-        <v>0.49055456299294198</v>
+        <v>-3.6023073536144201</v>
       </c>
       <c r="F93">
         <f t="shared" si="5"/>
-        <v>1.3418666117906899</v>
+        <v>1.0620996283442099</v>
       </c>
       <c r="G93" t="str">
         <f t="shared" si="6"/>
-        <v>0.490554562992942+1.34186661179069i</v>
+        <v>-3.60230735361442+1.06209962834421i</v>
       </c>
       <c r="H93" t="str">
         <f t="shared" si="7"/>
@@ -7079,19 +7081,19 @@
     </row>
     <row r="94" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D94" s="3" t="str">
-        <v>-1.64464867643698+0.875777454013299i</v>
+        <v>-0.594017920925936-0.450935755473508i</v>
       </c>
       <c r="E94">
         <f t="shared" si="4"/>
-        <v>-1.6446486764369801</v>
+        <v>-0.59401792092593597</v>
       </c>
       <c r="F94">
         <f t="shared" si="5"/>
-        <v>0.87577745401329898</v>
+        <v>-0.450935755473508</v>
       </c>
       <c r="G94" t="str">
         <f t="shared" si="6"/>
-        <v>-1.64464867643698+0.875777454013299i</v>
+        <v>-0.594017920925936-0.450935755473508i</v>
       </c>
       <c r="H94" t="str">
         <f t="shared" si="7"/>
@@ -7100,19 +7102,19 @@
     </row>
     <row r="95" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D95" s="3" t="str">
-        <v>0.0482871713537416-0.279065354898475i</v>
+        <v>0.129005718954389-0.390253891119822i</v>
       </c>
       <c r="E95">
         <f t="shared" si="4"/>
-        <v>4.8287171353741602E-2</v>
+        <v>0.129005718954389</v>
       </c>
       <c r="F95">
         <f t="shared" si="5"/>
-        <v>-0.279065354898475</v>
+        <v>-0.39025389111982201</v>
       </c>
       <c r="G95" t="str">
         <f t="shared" si="6"/>
-        <v>0.0482871713537416-0.279065354898475i</v>
+        <v>0.129005718954389-0.390253891119822i</v>
       </c>
       <c r="H95" t="str">
         <f t="shared" si="7"/>
@@ -7121,19 +7123,19 @@
     </row>
     <row r="96" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D96" s="3" t="str">
-        <v>2.54479266579765-0.557522898534096i</v>
+        <v>-0.547510922978154-0.393815230573597i</v>
       </c>
       <c r="E96">
         <f t="shared" si="4"/>
-        <v>2.5447926657976501</v>
+        <v>-0.54751092297815396</v>
       </c>
       <c r="F96">
         <f t="shared" si="5"/>
-        <v>-0.55752289853409598</v>
+        <v>-0.39381523057359702</v>
       </c>
       <c r="G96" t="str">
         <f t="shared" si="6"/>
-        <v>2.54479266579765-0.557522898534096i</v>
+        <v>-0.547510922978154-0.393815230573597i</v>
       </c>
       <c r="H96" t="str">
         <f t="shared" si="7"/>
@@ -7142,19 +7144,19 @@
     </row>
     <row r="97" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D97" s="3" t="str">
-        <v>0.57968986927194-0.295533148506069i</v>
+        <v>0.453778565648986+0.384786812571133i</v>
       </c>
       <c r="E97">
         <f t="shared" si="4"/>
-        <v>0.57968986927193999</v>
+        <v>0.453778565648986</v>
       </c>
       <c r="F97">
         <f t="shared" si="5"/>
-        <v>-0.29553314850606899</v>
+        <v>0.38478681257113301</v>
       </c>
       <c r="G97" t="str">
         <f t="shared" si="6"/>
-        <v>0.57968986927194-0.295533148506069i</v>
+        <v>0.453778565648986+0.384786812571133i</v>
       </c>
       <c r="H97" t="str">
         <f t="shared" si="7"/>
@@ -7163,19 +7165,19 @@
     </row>
     <row r="98" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D98" s="3" t="str">
-        <v>-0.474035243217465-0.61883179349525i</v>
+        <v>-0.41656051808689-0.4278506203652i</v>
       </c>
       <c r="E98">
         <f t="shared" si="4"/>
-        <v>-0.47403524321746499</v>
+        <v>-0.41656051808688999</v>
       </c>
       <c r="F98">
         <f t="shared" si="5"/>
-        <v>-0.61883179349524997</v>
+        <v>-0.4278506203652</v>
       </c>
       <c r="G98" t="str">
         <f t="shared" si="6"/>
-        <v>-0.474035243217465-0.61883179349525i</v>
+        <v>-0.41656051808689-0.4278506203652i</v>
       </c>
       <c r="H98" t="str">
         <f t="shared" si="7"/>
@@ -7184,19 +7186,19 @@
     </row>
     <row r="99" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D99" s="3" t="str">
-        <v>-0.650866851666247-1.56896468746556i</v>
+        <v>-0.603375046483674+1.08032098320429i</v>
       </c>
       <c r="E99">
         <f t="shared" si="4"/>
-        <v>-0.65086685166624703</v>
+        <v>-0.60337504648367402</v>
       </c>
       <c r="F99">
         <f t="shared" si="5"/>
-        <v>-1.5689646874655601</v>
+        <v>1.0803209832042899</v>
       </c>
       <c r="G99" t="str">
         <f t="shared" si="6"/>
-        <v>-0.650866851666247-1.56896468746556i</v>
+        <v>-0.603375046483674+1.08032098320429i</v>
       </c>
       <c r="H99" t="str">
         <f t="shared" si="7"/>
@@ -7205,19 +7207,19 @@
     </row>
     <row r="100" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D100" s="3" t="str">
-        <v>-0.718194259287174+2.84555896199134i</v>
+        <v>-0.454192557675401-2.39453674815223i</v>
       </c>
       <c r="E100">
         <f t="shared" si="4"/>
-        <v>-0.71819425928717395</v>
+        <v>-0.45419255767540101</v>
       </c>
       <c r="F100">
         <f t="shared" si="5"/>
-        <v>2.84555896199134</v>
+        <v>-2.3945367481522299</v>
       </c>
       <c r="G100" t="str">
         <f t="shared" si="6"/>
-        <v>-0.718194259287174+2.84555896199134i</v>
+        <v>-0.454192557675401-2.39453674815223i</v>
       </c>
       <c r="H100" t="str">
         <f t="shared" si="7"/>
@@ -7226,19 +7228,19 @@
     </row>
     <row r="101" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D101" s="3" t="str">
-        <v>-1.16227105827495+1.29015900224711i</v>
+        <v>0.396953027379582-1.31310501993183i</v>
       </c>
       <c r="E101">
         <f t="shared" si="4"/>
-        <v>-1.16227105827495</v>
+        <v>0.39695302737958199</v>
       </c>
       <c r="F101">
         <f t="shared" si="5"/>
-        <v>1.2901590022471101</v>
+        <v>-1.3131050199318299</v>
       </c>
       <c r="G101" t="str">
         <f t="shared" si="6"/>
-        <v>-1.16227105827495+1.29015900224711i</v>
+        <v>0.396953027379582-1.31310501993183i</v>
       </c>
       <c r="H101" t="str">
         <f t="shared" si="7"/>
@@ -7247,19 +7249,19 @@
     </row>
     <row r="102" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D102" s="3" t="str">
-        <v>-1.67403647949503+2.22322940717509i</v>
+        <v>0.7094466786735+0.154441507015508i</v>
       </c>
       <c r="E102">
         <f t="shared" si="4"/>
-        <v>-1.67403647949503</v>
+        <v>0.70944667867349998</v>
       </c>
       <c r="F102">
         <f t="shared" si="5"/>
-        <v>2.22322940717509</v>
+        <v>0.15444150701550799</v>
       </c>
       <c r="G102" t="str">
         <f t="shared" si="6"/>
-        <v>-1.67403647949503+2.22322940717509i</v>
+        <v>0.7094466786735+0.154441507015508i</v>
       </c>
       <c r="H102" t="str">
         <f t="shared" si="7"/>
@@ -22442,8 +22444,8 @@
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" customWidth="1"/>
     <col min="8" max="8" width="12.109375" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22504,7 +22506,14 @@
       <c r="H6" t="str">
         <v>1968-07-13</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="J6" s="10">
+        <f>DATEVALUE(G6)</f>
+        <v>23054</v>
+      </c>
+      <c r="K6" s="10">
+        <f>DATEVALUE(H6)</f>
+        <v>25032</v>
+      </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
@@ -22520,6 +22529,14 @@
       </c>
       <c r="H7" t="str">
         <v>1968-07-13</v>
+      </c>
+      <c r="J7" s="10">
+        <f>DATEVALUE(G7)</f>
+        <v>23054</v>
+      </c>
+      <c r="K7" s="10">
+        <f>DATEVALUE(H7)</f>
+        <v>25032</v>
       </c>
     </row>
   </sheetData>
@@ -27429,7 +27446,8 @@
       </c>
       <c r="C2" t="str" cm="1">
         <f t="array" ref="C2">TRANSPOSE(_xll.RScript.Evaluate(B2, TRUE))</f>
-        <v>OK</v>
+        <v xml:space="preserve">Exception: Error in library(complexplus) : there is no package called 'complexplus'
+</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.3">
